--- a/VerveStacks_GHA_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC409A6E-A244-43A1-BEF4-882C64829FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB64E6-21F2-4232-8A5C-5C1E1E9B7987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5023,7 +5023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD1EC88-AA63-49C3-A744-D80FD2C15B83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FF6ABF-A368-4F15-A7E9-BFCD818F35B5}">
   <dimension ref="B3:I13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_GHA_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_GHA_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB64E6-21F2-4232-8A5C-5C1E1E9B7987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEF8570-B9F2-44D8-8F55-477F51D0CAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5023,7 +5023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FF6ABF-A368-4F15-A7E9-BFCD818F35B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F53E84C-5AC0-4460-A66B-657E57BEE08E}">
   <dimension ref="B3:I13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
